--- a/public/ValueSet-body-temperature-measurement-location.xlsx
+++ b/public/ValueSet-body-temperature-measurement-location.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:28:41-06:00</t>
+    <t>2026-09-10T16:32:51-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/ValueSet-body-temperature-measurement-location.xlsx
+++ b/public/ValueSet-body-temperature-measurement-location.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Body Temperature Measurement Location Codes</t>
+    <t>Body Temperature Measurement Location Value Set</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T16:07:18-05:00</t>
+    <t>2026-10-08T19:53:09-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
